--- a/data/performance/daily/signal_list_2026-06-04.xlsx
+++ b/data/performance/daily/signal_list_2026-06-04.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-06-04.xlsx
+++ b/data/performance/daily/signal_list_2026-06-04.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-06-04.xlsx
+++ b/data/performance/daily/signal_list_2026-06-04.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -461,9 +461,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,7 +494,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -518,15 +519,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -563,12 +569,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,17 +611,22 @@
       <c r="G6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,12 +663,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -689,12 +710,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -726,17 +752,22 @@
       <c r="G9" s="4" t="n">
         <v>-14.41</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -773,12 +804,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -810,17 +846,22 @@
       <c r="G11" s="4" t="n">
         <v>-0.98</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -857,12 +898,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -879,7 +925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -889,9 +935,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -921,7 +968,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -946,15 +993,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -991,12 +1043,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1028,17 +1085,22 @@
       <c r="G6" s="4" t="n">
         <v>-0.72</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1075,12 +1137,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1112,17 +1179,22 @@
       <c r="G8" s="4" t="n">
         <v>-1.27</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1154,17 +1226,22 @@
       <c r="G9" s="4" t="n">
         <v>-10.53</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1196,17 +1273,22 @@
       <c r="G10" s="4" t="n">
         <v>-14.65</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1243,12 +1325,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1280,17 +1367,22 @@
       <c r="G12" s="4" t="n">
         <v>-14.97</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1327,12 +1419,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1364,17 +1461,22 @@
       <c r="G14" s="4" t="n">
         <v>-8.449999999999999</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1411,12 +1513,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1448,17 +1555,22 @@
       <c r="G16" s="4" t="n">
         <v>-14.41</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1490,17 +1602,22 @@
       <c r="G17" s="4" t="n">
         <v>-12.5</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1532,17 +1649,22 @@
       <c r="G18" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1579,12 +1701,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1616,17 +1743,22 @@
       <c r="G20" s="4" t="n">
         <v>-0.57</v>
       </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1658,17 +1790,22 @@
       <c r="G21" s="4" t="n">
         <v>-14.88</v>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1700,17 +1837,22 @@
       <c r="G22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1742,17 +1884,22 @@
       <c r="G23" s="4" t="n">
         <v>-3.85</v>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1789,12 +1936,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1831,12 +1983,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-06-04.xlsx
+++ b/data/performance/daily/signal_list_2026-06-04.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -459,12 +459,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,45 +495,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -553,33 +559,36 @@
         <v>156</v>
       </c>
       <c r="D5" t="n">
+        <v>156</v>
+      </c>
+      <c r="E5" t="n">
         <v>153</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>156</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>-1.92</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -603,30 +612,33 @@
         <v>1115</v>
       </c>
       <c r="E6" t="n">
+        <v>1115</v>
+      </c>
+      <c r="F6" t="n">
         <v>1120</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>0.45</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,33 +659,36 @@
         <v>2620</v>
       </c>
       <c r="D7" t="n">
+        <v>2620</v>
+      </c>
+      <c r="E7" t="n">
         <v>2450</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>2620</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>-6.49</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -694,33 +709,36 @@
         <v>8100</v>
       </c>
       <c r="D8" t="n">
+        <v>8100</v>
+      </c>
+      <c r="E8" t="n">
         <v>8175</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>8900</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>9.880000000000001</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -741,33 +759,36 @@
         <v>225.5</v>
       </c>
       <c r="D9" t="n">
+        <v>226</v>
+      </c>
+      <c r="E9" t="n">
         <v>193</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>228</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>-14.41</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -788,33 +809,36 @@
         <v>980</v>
       </c>
       <c r="D10" t="n">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="E10" t="n">
         <v>980</v>
       </c>
-      <c r="F10" s="4" t="n">
-        <v>0</v>
+      <c r="F10" t="n">
+        <v>980</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H10" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -835,33 +859,36 @@
         <v>510</v>
       </c>
       <c r="D11" t="n">
+        <v>510</v>
+      </c>
+      <c r="E11" t="n">
         <v>505</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>515</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>0.98</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>-0.98</v>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -882,33 +909,36 @@
         <v>1030</v>
       </c>
       <c r="D12" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E12" t="n">
         <v>1000</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>1025</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>-0.49</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>-2.91</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -925,7 +955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -933,12 +963,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -968,45 +999,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1027,33 +1063,36 @@
         <v>610</v>
       </c>
       <c r="D5" t="n">
+        <v>635</v>
+      </c>
+      <c r="E5" t="n">
         <v>715</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>740</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>21.31</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>17.21</v>
       </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1074,33 +1113,36 @@
         <v>276</v>
       </c>
       <c r="D6" t="n">
+        <v>280</v>
+      </c>
+      <c r="E6" t="n">
         <v>274</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>280</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>1.45</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>-0.72</v>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1121,33 +1163,36 @@
         <v>334</v>
       </c>
       <c r="D7" t="n">
+        <v>288.75</v>
+      </c>
+      <c r="E7" t="n">
         <v>302.67</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>307.89</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>-7.82</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>-9.380000000000001</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1168,33 +1213,36 @@
         <v>5900</v>
       </c>
       <c r="D8" t="n">
+        <v>6100</v>
+      </c>
+      <c r="E8" t="n">
         <v>5825</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>6100</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>3.39</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>-1.27</v>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1215,33 +1263,36 @@
         <v>114</v>
       </c>
       <c r="D9" t="n">
+        <v>114</v>
+      </c>
+      <c r="E9" t="n">
         <v>102</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>116</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>1.75</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>-10.53</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1262,33 +1313,36 @@
         <v>1365</v>
       </c>
       <c r="D10" t="n">
+        <v>1370</v>
+      </c>
+      <c r="E10" t="n">
         <v>1165</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>1375</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>0.73</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>-14.65</v>
       </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1309,33 +1363,36 @@
         <v>480</v>
       </c>
       <c r="D11" t="n">
+        <v>432</v>
+      </c>
+      <c r="E11" t="n">
         <v>434</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>442</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>-7.92</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>-9.58</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1356,33 +1413,36 @@
         <v>167</v>
       </c>
       <c r="D12" t="n">
+        <v>167</v>
+      </c>
+      <c r="E12" t="n">
         <v>142</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>182</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>8.98</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>-14.97</v>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1403,33 +1463,36 @@
         <v>194</v>
       </c>
       <c r="D13" t="n">
-        <v>258</v>
+        <v>208</v>
       </c>
       <c r="E13" t="n">
         <v>258</v>
       </c>
-      <c r="F13" s="4" t="n">
-        <v>32.99</v>
+      <c r="F13" t="n">
+        <v>258</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>32.99</v>
       </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H13" s="4" t="n">
+        <v>32.99</v>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1450,33 +1513,36 @@
         <v>71</v>
       </c>
       <c r="D14" t="n">
+        <v>72</v>
+      </c>
+      <c r="E14" t="n">
         <v>65</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>73</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>2.82</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>-8.449999999999999</v>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1497,33 +1563,36 @@
         <v>8100</v>
       </c>
       <c r="D15" t="n">
+        <v>8100</v>
+      </c>
+      <c r="E15" t="n">
         <v>8175</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>8900</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>9.880000000000001</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1544,33 +1613,36 @@
         <v>225.5</v>
       </c>
       <c r="D16" t="n">
+        <v>226</v>
+      </c>
+      <c r="E16" t="n">
         <v>193</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>228</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>-14.41</v>
       </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1594,30 +1666,33 @@
         <v>91</v>
       </c>
       <c r="E17" t="n">
+        <v>91</v>
+      </c>
+      <c r="F17" t="n">
         <v>121</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>16.35</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>-12.5</v>
       </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1638,33 +1713,36 @@
         <v>280</v>
       </c>
       <c r="D18" t="n">
+        <v>296</v>
+      </c>
+      <c r="E18" t="n">
         <v>266</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>296</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>5.71</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1685,33 +1763,36 @@
         <v>143</v>
       </c>
       <c r="D19" t="n">
+        <v>149</v>
+      </c>
+      <c r="E19" t="n">
         <v>156</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>157</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>9.789999999999999</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>9.09</v>
       </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1735,30 +1816,33 @@
         <v>348</v>
       </c>
       <c r="E20" t="n">
+        <v>348</v>
+      </c>
+      <c r="F20" t="n">
         <v>362</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>3.43</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>-0.57</v>
       </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1779,33 +1863,36 @@
         <v>121</v>
       </c>
       <c r="D21" t="n">
+        <v>115</v>
+      </c>
+      <c r="E21" t="n">
         <v>103</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>138</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="G21" s="4" t="n">
         <v>14.05</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="H21" s="4" t="n">
         <v>-14.88</v>
       </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1826,33 +1913,36 @@
         <v>725</v>
       </c>
       <c r="D22" t="n">
+        <v>720</v>
+      </c>
+      <c r="E22" t="n">
         <v>725</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>770</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>6.21</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="H22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1873,33 +1963,36 @@
         <v>4160</v>
       </c>
       <c r="D23" t="n">
+        <v>4150</v>
+      </c>
+      <c r="E23" t="n">
         <v>4000</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>4180</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>0.48</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="H23" s="4" t="n">
         <v>-3.85</v>
       </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1920,33 +2013,36 @@
         <v>1030</v>
       </c>
       <c r="D24" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E24" t="n">
         <v>1000</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>1025</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="G24" s="4" t="n">
         <v>-0.49</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="H24" s="4" t="n">
         <v>-2.91</v>
       </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1967,33 +2063,36 @@
         <v>212</v>
       </c>
       <c r="D25" t="n">
+        <v>210</v>
+      </c>
+      <c r="E25" t="n">
         <v>216</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>218</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>2.83</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>1.89</v>
       </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
